--- a/ig/Bac-à-sable-dan/ValueSet-vs-edqm-all.xlsx
+++ b/ig/Bac-à-sable-dan/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T10:24:30+00:00</t>
+    <t>2024-11-25T16:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
